--- a/public/works/grid/two-source-recon-01.xlsx
+++ b/public/works/grid/two-source-recon-01.xlsx
@@ -355,7 +355,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E5F"/>
+        <fgColor rgb="FF464646"/>
       </patternFill>
     </fill>
     <fill>
